--- a/submit/CS106_F31_CN2 - Nhom 9/Danh_sach_nhom.xlsx
+++ b/submit/CS106_F31_CN2 - Nhom 9/Danh_sach_nhom.xlsx
@@ -1,70 +1,210 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tcdtist/dev/uit/cs106/assignments/Final/submit/CS106_F31_CN2 - Nhom 9/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8CD605-84B2-8043-938A-B63A79BB0401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="67200" windowHeight="37180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách nhóm 9" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Danh sách nhóm 9" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+  <si>
+    <t>Môn học: Trí tuệ Nhân tạo (CS106.F31.CN2.TTNT) — Đề tài 7: Financial Fraud Detection — Nhóm 9</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Họ và Tên</t>
+  </si>
+  <si>
+    <t>MSSV</t>
+  </si>
+  <si>
+    <t>Lớp</t>
+  </si>
+  <si>
+    <t>Vai trò</t>
+  </si>
+  <si>
+    <t>Nhiệm vụ chính phụ trách</t>
+  </si>
+  <si>
+    <t>Trần Hoàng Hôn</t>
+  </si>
+  <si>
+    <t>26410046</t>
+  </si>
+  <si>
+    <t>CS106.F31.CN2.TTNT</t>
+  </si>
+  <si>
+    <t>Trưởng nhóm</t>
+  </si>
+  <si>
+    <t>Quản lý tiến độ đồ án; điều phối chung các sprint; hỗ trợ slide thuyết trình PPT và hoàn thiện hồ sơ đóng gói bài nộp</t>
+  </si>
+  <si>
+    <t>Đặng Chí Thanh</t>
+  </si>
+  <si>
+    <t>25730067</t>
+  </si>
+  <si>
+    <t>Thành viên</t>
+  </si>
+  <si>
+    <t>Thiết kế kiến trúc hệ thống; Khám phá dữ liệu (EDA), Tiền xử lý dữ liệu và trích xuất 14 đặc trưng; Notebook 01</t>
+  </si>
+  <si>
+    <t>Hoàng Cao Sơn</t>
+  </si>
+  <si>
+    <t>25730061</t>
+  </si>
+  <si>
+    <t>Phân tích và xử lý mất cân bằng lớp (SMOTENC, ADASYN); Nghiên cứu, huấn luyện và tối ưu mô hình Random Forest; Notebook 02 &amp; 03</t>
+  </si>
+  <si>
+    <t>Bùi Thị Mỷ Cẩm</t>
+  </si>
+  <si>
+    <t>25730013</t>
+  </si>
+  <si>
+    <t>Nghiên cứu, huấn luyện và tối ưu mô hình XGBoost; Xây dựng mạng nơ-ron Autoencoder phát hiện bất thường; Notebook 04 &amp; 05</t>
+  </si>
+  <si>
+    <t>Nguyễn Duy Khang</t>
+  </si>
+  <si>
+    <t>26410055</t>
+  </si>
+  <si>
+    <t>Xây dựng pipeline đánh giá và đối sánh hiệu năng chéo đa mô hình (ROC-AUC, PR-AUC, F1-Score); Xuất đồ thị đối chứng và bảng so sánh; Notebook 06</t>
+  </si>
+  <si>
+    <t>Vũ Văn Duy</t>
+  </si>
+  <si>
+    <t>26410031</t>
+  </si>
+  <si>
+    <t>Biên soạn tài liệu Báo cáo học thuật chính thức (Chương 1–7); Tổng hợp cơ sở lý thuyết, phân tích kết quả thực nghiệm và tính toán khoảng tin cậy thống kê</t>
+  </si>
+  <si>
+    <t>Phạm Thành Trung</t>
+  </si>
+  <si>
+    <t>26410141</t>
+  </si>
+  <si>
+    <t>Thiết kế và phát triển ứng dụng Web tương tác Streamlit Demo; Tích hợp mô hình suy luận thời gian thực; Sản xuất video clip minh họa sản phẩm</t>
+  </si>
+  <si>
+    <t>* Ghi chú: 100% thành viên trong nhóm tham gia đóng góp trách nhiệm và đồng thuận với toàn bộ kết quả nghiệm thu.</t>
+  </si>
+  <si>
+    <t>BẢNG DANH SÁCH NHÓM VÀ PHÂN CÔNG NHIỆM VỤ</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="000F2C59"/>
-      <sz val="14"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="004B5563"/>
-      <sz val="11"/>
+      <family val="1"/>
     </font>
     <font>
+      <sz val="13"/>
+      <color rgb="FF1E293B"/>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <family val="1"/>
     </font>
     <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF475569"/>
       <name val="Times New Roman"/>
-      <sz val="11"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF0F2C59"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF64748B"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F2C59"/>
-        <bgColor rgb="000F2C59"/>
+        <fgColor rgb="FF0F2C59"/>
+        <bgColor rgb="FF0F2C59"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,118 +218,71 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -477,241 +570,214 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="74" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DANH SÁCH THÀNH VIÊN VÀ PHÂN CÔNG ĐỒ ÁN CUỐI KỲ</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Môn: Trí tuệ Nhân tạo (CS106.F31.CN2.TTNT) — Đề tài 7: Financial Fraud Detection — Nhóm 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Họ và tên</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>MSSV</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Lớp</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Nhiệm vụ và Đóng góp chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Trần Hoàng Hôn</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>26410046</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS106.F31.CN2</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Nhóm trưởng, Quản lý tiến độ, Slide thuyết trình PPT, Đóng gói bài nộp</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Đặng Chí Thanh</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>25730067</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>CS106.F31.CN2</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>EDA, Tiền xử lý dữ liệu, Trích xuất 14 đặc trưng miền kế toán, Notebook 01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Hoàng Cao Sơn</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>25730061</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>CS106.F31.CN2</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Xử lý mất cân bằng lớp (SMOTENC/ADASYN), Random Forest, Notebook 02 &amp; 03</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Bùi Thị Mỷ Cẩm</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>25730013</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>CS106.F31.CN2</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Mô hình XGBoost, Autoencoder Anomaly Detection, Notebook 04 &amp; 05</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="E4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Nguyễn Duy Khang</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>26410055</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>CS106.F31.CN2</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Đánh giá đối sánh hiệu năng mô hình (ROC-AUC, PR-AUC, F1), Notebook 06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="F4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Vũ Văn Duy</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>26410031</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>CS106.F31.CN2</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Biên soạn Báo cáo học thuật (Chương 1–7), Phân tích khoảng tin cậy thống kê</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="n">
+    </row>
+    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Phạm Thành Trung</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>26410141</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>CS106.F31.CN2</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Thiết kế &amp; Triển khai Demo UI Streamlit, Video clip thuyết minh demo 5.5 phút</t>
-        </is>
-      </c>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="47" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="7">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
